--- a/public/templates/amo-exemple.xlsx
+++ b/public/templates/amo-exemple.xlsx
@@ -1,30 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Src\Beta.gouv\fonds-prevention-argile\public\templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313ED931-84A0-48FB-9CC6-A0E39558892B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840"/>
   </bookViews>
   <sheets>
-    <sheet name="Table1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Table1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>departements</t>
   </si>
   <si>
+    <t>epci</t>
+  </si>
+  <si>
     <t>nom</t>
   </si>
   <si>
@@ -40,6 +37,9 @@
     <t>adresse</t>
   </si>
   <si>
+    <t>horaires</t>
+  </si>
+  <si>
     <t>siret</t>
   </si>
   <si>
@@ -55,6 +55,9 @@
     <t>12 rue de la Construction, 75001 Paris</t>
   </si>
   <si>
+    <t>Du lundi au vendredi 9h - 12h / 14h - 17h</t>
+  </si>
+  <si>
     <t>Indre 36</t>
   </si>
   <si>
@@ -67,6 +70,12 @@
     <t>45 avenue des Fondations, 69001 Lyon</t>
   </si>
   <si>
+    <t>Du mardi au vendredi 8h30 - 12h / 13h - 17h30</t>
+  </si>
+  <si>
+    <t>243600327;200068872;200041317</t>
+  </si>
+  <si>
     <t>Argile &amp; Compagnie</t>
   </si>
   <si>
@@ -76,6 +85,9 @@
     <t>8 impasse de la Terre, 32000 Ville</t>
   </si>
   <si>
+    <t>Lundi 13h - 17h30</t>
+  </si>
+  <si>
     <t>Anti-Fissure Express</t>
   </si>
   <si>
@@ -85,9 +97,15 @@
     <t>34 place du Renforcement, 31000 Toulouse</t>
   </si>
   <si>
+    <t>Du lundi au vendredi 9h - 18h</t>
+  </si>
+  <si>
     <t>Gers 32</t>
   </si>
   <si>
+    <t>200034726;200042372;248200016;200023620;200066926;243200391;243200599</t>
+  </si>
+  <si>
     <t>Cabinet Terre Solide</t>
   </si>
   <si>
@@ -97,6 +115,9 @@
     <t>67 avenue de la Stabilité, 36000 Châteauroux</t>
   </si>
   <si>
+    <t>Sur rendez-vous uniquement</t>
+  </si>
+  <si>
     <t>AMO Maison Tranquille</t>
   </si>
   <si>
@@ -106,53 +127,47 @@
     <t>78 impasse du Repos Assuré, 36000 Châteauroux</t>
   </si>
   <si>
-    <t>epci</t>
-  </si>
-  <si>
-    <t>243600327;200068872;200041317</t>
-  </si>
-  <si>
-    <t>200034726;200042372;248200016;200023620;200066926;243200391;243200599</t>
+    <t>Du lundi au jeudi 9h - 17h / vendredi 9h - 12h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF3A3A3A"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF3A3A3A"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -168,7 +183,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -207,13 +222,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -232,38 +240,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -272,21 +289,13 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -582,231 +591,253 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="75.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" customWidth="1"/>
+    <col min="2" max="2" width="75.140625" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="64.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="40.7109375" customWidth="1"/>
+    <col min="8" max="8" width="45" customWidth="1"/>
+    <col min="9" max="9" width="29.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="19.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="11">
+        <v>102030405</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12">
+        <v>13002526500013</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="11">
+        <v>102030405</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2">
+        <v>55203253400646</v>
+      </c>
+    </row>
+    <row r="4" ht="20.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="11">
+        <v>102030405</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2">
+        <v>55204954702513</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="11">
+        <v>607080910</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="2">
+        <v>47250090600146</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="7">
-        <v>102030405</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="8">
-        <v>13002526500013</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7">
-        <v>102030405</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="B6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="11">
+        <v>607080910</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="2">
+        <v>35238011900034</v>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="15">
-        <v>55203253400646</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7">
-        <v>102030405</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="15">
-        <v>55204954702513</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6" t="s">
+      <c r="B7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="7">
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="11">
         <v>607080910</v>
       </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="15">
-        <v>47250090600146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="7">
-        <v>607080910</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="15">
-        <v>35238011900034</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="7">
-        <v>607080910</v>
-      </c>
       <c r="G7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="15">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="2">
         <v>34217127500329</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="13"/>
+    <row r="8" ht="18.75" customHeight="1" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="9"/>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="9"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="9"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="9"/>
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="9"/>
+      <c r="I12" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>